--- a/Essity modell.xlsx
+++ b/Essity modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECF6C5E-764E-9D47-94E3-04D2EB8DE757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF0F09-767D-1942-B414-529DFEC444D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25140" yWindow="500" windowWidth="26060" windowHeight="26740" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="230">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -717,6 +717,42 @@
   </si>
   <si>
     <t>Gearing</t>
+  </si>
+  <si>
+    <t>20.07.26: Essity kjøper tilbake 286 026 B-aksjer</t>
+  </si>
+  <si>
+    <t>27.07.26: Essity kjøper tilbake 280 871 B-aksjer</t>
+  </si>
+  <si>
+    <t>03.08.26: Essity kjøper tilbake 280 884 B-aksjer</t>
+  </si>
+  <si>
+    <t>10.08.26: Essity kjøper tilbake 277 688 B-aksjer</t>
+  </si>
+  <si>
+    <t>17.08.26: Essity kjøper tilbake 275 953 B-aksjer</t>
+  </si>
+  <si>
+    <t>24.08.26: Essity kjøper tilbake 282 790 B-aksjer</t>
+  </si>
+  <si>
+    <t>31.08.26: Essity kjøper tilbake 267 157 B-aksjer</t>
+  </si>
+  <si>
+    <t>07.09.26: Essity kjøper tilbake 273 715 B-aksjer</t>
+  </si>
+  <si>
+    <t>14.09.26: Essity kjøper tilbake 362 503 B-aksjer</t>
+  </si>
+  <si>
+    <t>21.09.26: Essity sin CFO planlegger å gi seg i rollen ila 2027</t>
+  </si>
+  <si>
+    <t>21.09.26: Essity kjøper tilbake 397 967 B-aksjer</t>
+  </si>
+  <si>
+    <t>28.09.26: Essity kjøper tilbake 402 677 B-aksjer</t>
   </si>
 </sst>
 </file>
@@ -728,7 +764,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="172" formatCode="0.0\ %"/>
+    <numFmt numFmtId="167" formatCode="0.0\ %"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -956,7 +992,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1035,19 +1071,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2260,7 +2301,7 @@
     <col min="8" max="17" width="10.83203125" style="55"/>
     <col min="18" max="18" width="33.5" style="55" customWidth="1"/>
     <col min="19" max="19" width="29.6640625" style="59" customWidth="1"/>
-    <col min="20" max="20" width="28.1640625" style="64" customWidth="1"/>
+    <col min="20" max="20" width="28.1640625" style="75" customWidth="1"/>
     <col min="21" max="21" width="40.6640625" style="57" customWidth="1"/>
     <col min="22" max="22" width="47.83203125" style="57" customWidth="1"/>
     <col min="23" max="23" width="27.33203125" style="57" customWidth="1"/>
@@ -2277,7 +2318,7 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
+      <c r="T1" s="73"/>
       <c r="U1" s="55"/>
       <c r="V1" s="55"/>
       <c r="W1" s="55"/>
@@ -2285,7 +2326,7 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
+      <c r="T2" s="73"/>
       <c r="U2" s="55"/>
       <c r="V2" s="55"/>
       <c r="W2" s="55"/>
@@ -2295,7 +2336,7 @@
       <c r="S3" s="54" t="s">
         <v>185</v>
       </c>
-      <c r="T3" s="55"/>
+      <c r="T3" s="73"/>
       <c r="U3" s="55"/>
       <c r="V3" s="55"/>
       <c r="W3" s="55"/>
@@ -2308,7 +2349,7 @@
       <c r="S4" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="T4" s="61" t="s">
+      <c r="T4" s="74" t="s">
         <v>187</v>
       </c>
       <c r="U4" s="61" t="s">
@@ -2343,7 +2384,7 @@
       <c r="S5" s="60">
         <v>46160</v>
       </c>
-      <c r="T5" s="57">
+      <c r="T5" s="75">
         <v>198501</v>
       </c>
       <c r="U5" s="57">
@@ -2379,7 +2420,7 @@
       <c r="S6" s="59">
         <v>46167</v>
       </c>
-      <c r="T6" s="57">
+      <c r="T6" s="75">
         <v>324469</v>
       </c>
       <c r="U6" s="57">
@@ -2417,7 +2458,7 @@
       <c r="S7" s="59">
         <v>46174</v>
       </c>
-      <c r="T7" s="57">
+      <c r="T7" s="75">
         <v>311814</v>
       </c>
       <c r="U7" s="57">
@@ -2455,7 +2496,7 @@
       <c r="S8" s="59">
         <v>46181</v>
       </c>
-      <c r="T8" s="57">
+      <c r="T8" s="75">
         <v>319589</v>
       </c>
       <c r="U8" s="57">
@@ -2492,7 +2533,7 @@
       <c r="S9" s="59">
         <v>46188</v>
       </c>
-      <c r="T9" s="57">
+      <c r="T9" s="75">
         <v>307819</v>
       </c>
       <c r="U9" s="57">
@@ -2528,7 +2569,7 @@
       <c r="S10" s="59">
         <v>46195</v>
       </c>
-      <c r="T10" s="57">
+      <c r="T10" s="75">
         <v>243164</v>
       </c>
       <c r="U10" s="57">
@@ -2565,7 +2606,7 @@
       <c r="S11" s="59">
         <v>46202</v>
       </c>
-      <c r="T11" s="57">
+      <c r="T11" s="75">
         <v>294782</v>
       </c>
       <c r="U11" s="57">
@@ -2603,7 +2644,7 @@
       <c r="S12" s="59">
         <v>46209</v>
       </c>
-      <c r="T12" s="57">
+      <c r="T12" s="75">
         <v>290631</v>
       </c>
       <c r="U12" s="57">
@@ -2641,7 +2682,7 @@
       <c r="S13" s="59">
         <v>46216</v>
       </c>
-      <c r="T13" s="57">
+      <c r="T13" s="75">
         <v>286149</v>
       </c>
       <c r="U13" s="57">
@@ -2675,6 +2716,23 @@
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S14" s="59">
+        <v>46223</v>
+      </c>
+      <c r="T14" s="75">
+        <v>286026</v>
+      </c>
+      <c r="U14" s="57">
+        <f>SUM(T5:T14)</f>
+        <v>2862944</v>
+      </c>
+      <c r="V14" s="57">
+        <v>79506289</v>
+      </c>
+      <c r="W14" s="57">
+        <f>SUM(V5:V14)</f>
+        <v>760033941</v>
+      </c>
       <c r="Y14" s="59">
         <v>45530</v>
       </c>
@@ -2694,6 +2752,23 @@
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S15" s="59">
+        <v>46230</v>
+      </c>
+      <c r="T15" s="75">
+        <v>280871</v>
+      </c>
+      <c r="U15" s="57">
+        <f>SUM(T5:T15)</f>
+        <v>3143815</v>
+      </c>
+      <c r="V15" s="57">
+        <v>78055194</v>
+      </c>
+      <c r="W15" s="57">
+        <f>SUM(V5:V15)</f>
+        <v>838089135</v>
+      </c>
       <c r="Y15" s="59">
         <v>45537</v>
       </c>
@@ -2713,6 +2788,23 @@
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S16" s="59">
+        <v>46237</v>
+      </c>
+      <c r="T16" s="75">
+        <v>280884</v>
+      </c>
+      <c r="U16" s="57">
+        <f>SUM(T5:T16)</f>
+        <v>3424699</v>
+      </c>
+      <c r="V16" s="57">
+        <v>78399793</v>
+      </c>
+      <c r="W16" s="57">
+        <f>SUM(V5:V16)</f>
+        <v>916488928</v>
+      </c>
       <c r="Y16" s="59">
         <v>45544</v>
       </c>
@@ -2735,9 +2827,23 @@
       <c r="A17" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="T17" s="57"/>
-      <c r="U17" s="55"/>
-      <c r="W17" s="55"/>
+      <c r="S17" s="59">
+        <v>46244</v>
+      </c>
+      <c r="T17" s="75">
+        <v>277688</v>
+      </c>
+      <c r="U17" s="57">
+        <f>SUM(T5:T17)</f>
+        <v>3702387</v>
+      </c>
+      <c r="V17" s="57">
+        <v>77757836</v>
+      </c>
+      <c r="W17" s="57">
+        <f>SUM(V5:V17)</f>
+        <v>994246764</v>
+      </c>
       <c r="X17" s="55"/>
       <c r="Y17" s="59">
         <v>45551</v>
@@ -2761,9 +2867,23 @@
       <c r="A18" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="T18" s="57"/>
-      <c r="U18" s="55"/>
-      <c r="W18" s="55"/>
+      <c r="S18" s="59">
+        <v>46251</v>
+      </c>
+      <c r="T18" s="75">
+        <v>275953</v>
+      </c>
+      <c r="U18" s="57">
+        <f>SUM(T5:T18)</f>
+        <v>3978340</v>
+      </c>
+      <c r="V18" s="57">
+        <v>76765020</v>
+      </c>
+      <c r="W18" s="57">
+        <f>SUM(V5:V18)</f>
+        <v>1071011784</v>
+      </c>
       <c r="X18" s="55"/>
       <c r="Y18" s="59">
         <v>45558</v>
@@ -2787,9 +2907,23 @@
       <c r="A19" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="T19" s="57"/>
-      <c r="U19" s="55"/>
-      <c r="W19" s="55"/>
+      <c r="S19" s="59">
+        <v>46258</v>
+      </c>
+      <c r="T19" s="75">
+        <v>282790</v>
+      </c>
+      <c r="U19" s="57">
+        <f>SUM(T5:T19)</f>
+        <v>4261130</v>
+      </c>
+      <c r="V19" s="57">
+        <v>76750144</v>
+      </c>
+      <c r="W19" s="57">
+        <f>SUM(V5:V19)</f>
+        <v>1147761928</v>
+      </c>
       <c r="X19" s="55"/>
       <c r="Y19" s="59">
         <v>45565</v>
@@ -2810,9 +2944,23 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="T20" s="57"/>
-      <c r="U20" s="55"/>
-      <c r="W20" s="55"/>
+      <c r="S20" s="59">
+        <v>46265</v>
+      </c>
+      <c r="T20" s="75">
+        <v>267157</v>
+      </c>
+      <c r="U20" s="57">
+        <f>SUM(T5:T20)</f>
+        <v>4528287</v>
+      </c>
+      <c r="V20" s="57">
+        <v>74940755</v>
+      </c>
+      <c r="W20" s="57">
+        <f>SUM(V5:V20)</f>
+        <v>1222702683</v>
+      </c>
       <c r="X20" s="55"/>
       <c r="Y20" s="59">
         <v>45572</v>
@@ -2836,9 +2984,23 @@
       <c r="A21" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="T21" s="57"/>
-      <c r="U21" s="55"/>
-      <c r="W21" s="55"/>
+      <c r="S21" s="59">
+        <v>46272</v>
+      </c>
+      <c r="T21" s="75">
+        <v>273715</v>
+      </c>
+      <c r="U21" s="57">
+        <f>SUM(T5:T21)</f>
+        <v>4802002</v>
+      </c>
+      <c r="V21" s="57">
+        <v>75551773</v>
+      </c>
+      <c r="W21" s="57">
+        <f>SUM(V5:V21)</f>
+        <v>1298254456</v>
+      </c>
       <c r="X21" s="55"/>
       <c r="Y21" s="59">
         <v>45579</v>
@@ -2859,6 +3021,23 @@
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S22" s="59">
+        <v>46279</v>
+      </c>
+      <c r="T22" s="75">
+        <v>362503</v>
+      </c>
+      <c r="U22" s="57">
+        <f>SUM(T5:T22)</f>
+        <v>5164505</v>
+      </c>
+      <c r="V22" s="57">
+        <v>96106904</v>
+      </c>
+      <c r="W22" s="57">
+        <f>SUM(V5:V22)</f>
+        <v>1394361360</v>
+      </c>
       <c r="Y22" s="59">
         <v>45586</v>
       </c>
@@ -2878,6 +3057,23 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S23" s="59">
+        <v>46286</v>
+      </c>
+      <c r="T23" s="75">
+        <v>397967</v>
+      </c>
+      <c r="U23" s="57">
+        <f>SUM(T5:T23)</f>
+        <v>5562472</v>
+      </c>
+      <c r="V23" s="57">
+        <v>105152187</v>
+      </c>
+      <c r="W23" s="57">
+        <f>SUM(V5:V23)</f>
+        <v>1499513547</v>
+      </c>
       <c r="Y23" s="59">
         <v>45593</v>
       </c>
@@ -2897,6 +3093,23 @@
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="S24" s="59">
+        <v>46293</v>
+      </c>
+      <c r="T24" s="75">
+        <v>402677</v>
+      </c>
+      <c r="U24" s="57">
+        <f>SUM(T5:T24)</f>
+        <v>5965149</v>
+      </c>
+      <c r="V24" s="57">
+        <v>105621968</v>
+      </c>
+      <c r="W24" s="57">
+        <f>SUM(V5:V24)</f>
+        <v>1605135515</v>
+      </c>
       <c r="Y24" s="59">
         <v>45600</v>
       </c>
@@ -2957,7 +3170,6 @@
       <c r="A27" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="T27" s="57"/>
       <c r="U27" s="55"/>
       <c r="W27" s="55"/>
       <c r="X27" s="55"/>
@@ -2981,7 +3193,7 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A28" s="55" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="Y28" s="59">
         <v>45628</v>
@@ -3003,7 +3215,7 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29" s="55" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="Y29" s="59">
         <v>45635</v>
@@ -3025,9 +3237,8 @@
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A30" s="55" t="s">
-        <v>213</v>
-      </c>
-      <c r="T30" s="57"/>
+        <v>227</v>
+      </c>
       <c r="U30" s="55"/>
       <c r="W30" s="55"/>
       <c r="X30" s="55"/>
@@ -3051,9 +3262,8 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A31" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="T31" s="57"/>
+        <v>226</v>
+      </c>
       <c r="U31" s="55"/>
       <c r="W31" s="55"/>
       <c r="X31" s="55"/>
@@ -3077,9 +3287,8 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="T32" s="57"/>
+        <v>225</v>
+      </c>
       <c r="U32" s="55"/>
       <c r="W32" s="55"/>
       <c r="X32" s="55"/>
@@ -3103,9 +3312,8 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="T33" s="57"/>
+        <v>224</v>
+      </c>
       <c r="U33" s="55"/>
       <c r="W33" s="55"/>
       <c r="X33" s="55"/>
@@ -3129,9 +3337,8 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="T34" s="57"/>
+        <v>223</v>
+      </c>
       <c r="U34" s="55"/>
       <c r="W34" s="55"/>
       <c r="X34" s="55"/>
@@ -3155,9 +3362,8 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="55" t="s">
-        <v>207</v>
-      </c>
-      <c r="T35" s="57"/>
+        <v>222</v>
+      </c>
       <c r="U35" s="55"/>
       <c r="W35" s="55"/>
       <c r="X35" s="55"/>
@@ -3181,9 +3387,8 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" s="55" t="s">
-        <v>206</v>
-      </c>
-      <c r="T36" s="57"/>
+        <v>221</v>
+      </c>
       <c r="U36" s="55"/>
       <c r="W36" s="55"/>
       <c r="X36" s="55"/>
@@ -3208,9 +3413,8 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="55" t="s">
-        <v>205</v>
-      </c>
-      <c r="T37" s="57"/>
+        <v>220</v>
+      </c>
       <c r="U37" s="55"/>
       <c r="W37" s="55"/>
       <c r="X37" s="55"/>
@@ -3235,9 +3439,8 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="T38" s="57"/>
+        <v>219</v>
+      </c>
       <c r="U38" s="55"/>
       <c r="W38" s="55"/>
       <c r="X38" s="55"/>
@@ -3262,9 +3465,8 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="T39" s="57"/>
+        <v>218</v>
+      </c>
       <c r="U39" s="55"/>
       <c r="W39" s="55"/>
       <c r="X39" s="55"/>
@@ -3288,9 +3490,8 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="T40" s="57"/>
+        <v>216</v>
+      </c>
       <c r="U40" s="55"/>
       <c r="W40" s="55"/>
       <c r="X40" s="55"/>
@@ -3314,9 +3515,8 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="T41" s="57"/>
+        <v>214</v>
+      </c>
       <c r="U41" s="55"/>
       <c r="W41" s="55"/>
       <c r="X41" s="55"/>
@@ -3340,9 +3540,8 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="T42" s="57"/>
+        <v>213</v>
+      </c>
       <c r="U42" s="55"/>
       <c r="W42" s="55"/>
       <c r="X42" s="55"/>
@@ -3366,9 +3565,8 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="T43" s="57"/>
+        <v>212</v>
+      </c>
       <c r="U43" s="55"/>
       <c r="W43" s="55"/>
       <c r="X43" s="55"/>
@@ -3392,9 +3590,8 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="T44" s="57"/>
+        <v>211</v>
+      </c>
       <c r="U44" s="55"/>
       <c r="W44" s="55"/>
       <c r="X44" s="55"/>
@@ -3416,9 +3613,8 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="T45" s="57"/>
+        <v>210</v>
+      </c>
       <c r="U45" s="55"/>
       <c r="W45" s="55"/>
       <c r="X45" s="55"/>
@@ -3442,9 +3638,8 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="T46" s="57"/>
+        <v>208</v>
+      </c>
       <c r="U46" s="55"/>
       <c r="W46" s="55"/>
       <c r="X46" s="55"/>
@@ -3468,9 +3663,8 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="T47" s="57"/>
+        <v>207</v>
+      </c>
       <c r="U47" s="55"/>
       <c r="W47" s="55"/>
       <c r="X47" s="55"/>
@@ -3494,9 +3688,8 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="T48" s="57"/>
+        <v>206</v>
+      </c>
       <c r="U48" s="55"/>
       <c r="W48" s="55"/>
       <c r="X48" s="55"/>
@@ -3520,9 +3713,8 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A49" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="T49" s="57"/>
+        <v>205</v>
+      </c>
       <c r="U49" s="55"/>
       <c r="W49" s="55"/>
       <c r="X49" s="55"/>
@@ -3546,9 +3738,8 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A50" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="T50" s="57"/>
+        <v>209</v>
+      </c>
       <c r="U50" s="55"/>
       <c r="W50" s="55"/>
       <c r="X50" s="55"/>
@@ -3572,9 +3763,8 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A51" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="T51" s="57"/>
+        <v>179</v>
+      </c>
       <c r="U51" s="55"/>
       <c r="W51" s="55"/>
       <c r="X51" s="55"/>
@@ -3598,7 +3788,7 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A52" s="55" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="Y52" s="59">
         <v>45824</v>
@@ -3620,7 +3810,7 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A53" s="55" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="Y53" s="59">
         <v>45831</v>
@@ -3642,7 +3832,7 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A54" s="55" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="Y54" s="59">
         <v>45838</v>
@@ -3664,7 +3854,7 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A55" s="55" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="Y55" s="59">
         <v>45845</v>
@@ -3686,7 +3876,7 @@
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A56" s="55" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="Y56" s="59">
         <v>45852</v>
@@ -3708,7 +3898,7 @@
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A57" s="55" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="Y57" s="59">
         <v>45859</v>
@@ -3730,7 +3920,7 @@
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58" s="55" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y58" s="59">
         <v>45866</v>
@@ -3752,7 +3942,7 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A59" s="55" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Y59" s="59">
         <v>45873</v>
@@ -3774,7 +3964,7 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60" s="55" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="Y60" s="59">
         <v>45880</v>
@@ -3796,7 +3986,7 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A61" s="55" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="Y61" s="59">
         <v>45887</v>
@@ -3818,7 +4008,7 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62" s="55" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="Y62" s="59">
         <v>45894</v>
@@ -3840,7 +4030,7 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63" s="55" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="Y63" s="59">
         <v>45901</v>
@@ -3862,7 +4052,7 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="55" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="Y64" s="59">
         <v>45908</v>
@@ -3884,7 +4074,7 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="55" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="Y65" s="59">
         <v>45915</v>
@@ -3906,7 +4096,7 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="55" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="Y66" s="59">
         <v>45922</v>
@@ -3928,7 +4118,7 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="55" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="Y67" s="59">
         <v>45929</v>
@@ -3950,7 +4140,7 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="55" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="Y68" s="59">
         <v>45936</v>
@@ -3972,7 +4162,7 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="55" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="Y69" s="59">
         <v>45943</v>
@@ -3994,7 +4184,7 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y70" s="59">
         <v>45950</v>
@@ -4016,7 +4206,7 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="55" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="Y71" s="59">
         <v>45957</v>
@@ -4038,7 +4228,7 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="55" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="Y72" s="59">
         <v>45964</v>
@@ -4059,6 +4249,9 @@
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A73" s="55" t="s">
+        <v>168</v>
+      </c>
       <c r="Y73" s="59">
         <v>45971</v>
       </c>
@@ -4078,6 +4271,9 @@
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A74" s="55" t="s">
+        <v>193</v>
+      </c>
       <c r="Y74" s="59">
         <v>45978</v>
       </c>
@@ -4097,6 +4293,9 @@
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A75" s="55" t="s">
+        <v>194</v>
+      </c>
       <c r="Y75" s="59">
         <v>45985</v>
       </c>
@@ -4116,6 +4315,9 @@
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A76" s="55" t="s">
+        <v>195</v>
+      </c>
       <c r="Y76" s="59">
         <v>45992</v>
       </c>
@@ -4135,6 +4337,9 @@
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A77" s="55" t="s">
+        <v>196</v>
+      </c>
       <c r="Y77" s="59">
         <v>45999</v>
       </c>
@@ -4154,6 +4359,9 @@
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A78" s="55" t="s">
+        <v>197</v>
+      </c>
       <c r="Y78" s="59">
         <v>46006</v>
       </c>
@@ -4173,6 +4381,9 @@
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A79" s="55" t="s">
+        <v>198</v>
+      </c>
       <c r="Y79" s="59">
         <v>46013</v>
       </c>
@@ -4192,6 +4403,9 @@
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A80" s="55" t="s">
+        <v>199</v>
+      </c>
       <c r="Y80" s="62">
         <v>46020</v>
       </c>
@@ -4210,7 +4424,10 @@
         <v>2376338594</v>
       </c>
     </row>
-    <row r="81" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A81" s="55" t="s">
+        <v>200</v>
+      </c>
       <c r="Y81" s="59">
         <v>46027</v>
       </c>
@@ -4229,7 +4446,10 @@
         <v>2387432033</v>
       </c>
     </row>
-    <row r="82" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A82" s="55" t="s">
+        <v>203</v>
+      </c>
       <c r="Y82" s="59">
         <v>46034</v>
       </c>
@@ -4248,7 +4468,10 @@
         <v>2402525572</v>
       </c>
     </row>
-    <row r="83" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A83" s="55" t="s">
+        <v>202</v>
+      </c>
       <c r="Y83" s="59">
         <v>46041</v>
       </c>
@@ -4267,7 +4490,10 @@
         <v>2420217480</v>
       </c>
     </row>
-    <row r="84" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A84" s="55" t="s">
+        <v>201</v>
+      </c>
       <c r="Y84" s="59">
         <v>46048</v>
       </c>
@@ -4286,7 +4512,7 @@
         <v>2604777220</v>
       </c>
     </row>
-    <row r="85" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y85" s="59">
         <v>46055</v>
       </c>
@@ -4305,7 +4531,7 @@
         <v>2648601836</v>
       </c>
     </row>
-    <row r="86" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y86" s="59">
         <v>46062</v>
       </c>
@@ -4324,7 +4550,7 @@
         <v>2667362337</v>
       </c>
     </row>
-    <row r="87" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y87" s="59">
         <v>46069</v>
       </c>
@@ -4343,7 +4569,7 @@
         <v>2685683858</v>
       </c>
     </row>
-    <row r="88" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y88" s="59">
         <v>46076</v>
       </c>
@@ -4362,7 +4588,7 @@
         <v>2703645345</v>
       </c>
     </row>
-    <row r="89" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y89" s="59">
         <v>46083</v>
       </c>
@@ -4381,7 +4607,7 @@
         <v>2764753691</v>
       </c>
     </row>
-    <row r="90" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y90" s="59">
         <v>46090</v>
       </c>
@@ -4400,7 +4626,7 @@
         <v>2829902498</v>
       </c>
     </row>
-    <row r="91" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y91" s="59">
         <v>46097</v>
       </c>
@@ -4419,7 +4645,7 @@
         <v>2895653175</v>
       </c>
     </row>
-    <row r="92" spans="25:29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Y92" s="60">
         <v>46104</v>
       </c>
@@ -4623,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>51</v>
@@ -4916,7 +5142,7 @@
       </c>
       <c r="B6" s="18">
         <f>B4*B5</f>
-        <v>186158.69999999998</v>
+        <v>179339.69999999998</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -5373,7 +5599,7 @@
       </c>
       <c r="B9" s="27">
         <f>B6-B7+B8</f>
-        <v>217728.69999999998</v>
+        <v>210909.69999999998</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>56</v>
@@ -5847,7 +6073,7 @@
       <c r="A12" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B12" s="67">
+      <c r="B12" s="66">
         <f>(B8-B7)/AK9</f>
         <v>1.7471739171340381</v>
       </c>
@@ -7885,591 +8111,591 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="68"/>
-      <c r="C20" s="69" t="s">
+    <row r="20" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="67"/>
+      <c r="C20" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="69">
+      <c r="H20" s="68">
         <f t="shared" ref="H20:R20" si="40">(H4-D4)/D4</f>
         <v>0.25145039503221478</v>
       </c>
-      <c r="I20" s="69">
+      <c r="I20" s="68">
         <f t="shared" si="40"/>
         <v>0.15821666798491918</v>
       </c>
-      <c r="J20" s="69">
+      <c r="J20" s="68">
         <f t="shared" si="40"/>
         <v>8.4943528883791669E-2</v>
       </c>
-      <c r="K20" s="69">
+      <c r="K20" s="68">
         <f t="shared" si="40"/>
         <v>-1.0920309044745967E-4</v>
       </c>
-      <c r="L20" s="69">
+      <c r="L20" s="68">
         <f t="shared" si="40"/>
         <v>-0.18813772538787682</v>
       </c>
-      <c r="M20" s="69">
+      <c r="M20" s="68">
         <f t="shared" si="40"/>
         <v>-0.16646938310949239</v>
       </c>
-      <c r="N20" s="69">
+      <c r="N20" s="68">
         <f t="shared" si="40"/>
         <v>-0.16642154609798696</v>
       </c>
-      <c r="O20" s="69">
+      <c r="O20" s="68">
         <f t="shared" si="40"/>
         <v>3.2218430034129691E-2</v>
       </c>
-      <c r="P20" s="69">
+      <c r="P20" s="68">
         <f t="shared" si="40"/>
         <v>3.6154949784791965E-3</v>
       </c>
-      <c r="Q20" s="69">
+      <c r="Q20" s="68">
         <f t="shared" si="40"/>
         <v>-6.6417237894966813E-2</v>
       </c>
-      <c r="R20" s="69">
+      <c r="R20" s="68">
         <f t="shared" si="40"/>
         <v>-4.5101174394883391E-2</v>
       </c>
-      <c r="S20" s="69">
+      <c r="S20" s="68">
         <f>(S4-O4)/O4</f>
         <v>-8.2264250760481411E-2</v>
       </c>
-      <c r="T20" s="69">
+      <c r="T20" s="68">
         <f>(T4-P4)/P4</f>
         <v>-5.1435269899359558E-2</v>
       </c>
-      <c r="U20" s="69">
+      <c r="U20" s="68">
         <f>(U4-Q4)/Q4</f>
         <v>2.5625274243089073E-2</v>
       </c>
-      <c r="V20" s="69"/>
-      <c r="W20" s="69"/>
-      <c r="X20" s="69"/>
-      <c r="Y20" s="69"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="69">
+      <c r="V20" s="68"/>
+      <c r="W20" s="68"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="68"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="68">
         <f t="shared" ref="AA20:AG20" si="41">(AA4-Z4)/Z4</f>
         <v>2.7598737299404177E-2</v>
       </c>
-      <c r="AB20" s="69">
+      <c r="AB20" s="68">
         <f t="shared" si="41"/>
         <v>7.9288409490507514E-2</v>
       </c>
-      <c r="AC20" s="69">
+      <c r="AC20" s="68">
         <f t="shared" si="41"/>
         <v>8.4519287969615151E-2</v>
       </c>
-      <c r="AD20" s="69">
+      <c r="AD20" s="68">
         <f t="shared" si="41"/>
         <v>8.8396624472573834E-2</v>
       </c>
-      <c r="AE20" s="69">
+      <c r="AE20" s="68">
         <f t="shared" si="41"/>
         <v>-5.6003101376235702E-2</v>
       </c>
-      <c r="AF20" s="69">
+      <c r="AF20" s="68">
         <f t="shared" si="41"/>
         <v>9.4454300545370915E-4</v>
       </c>
-      <c r="AG20" s="69">
+      <c r="AG20" s="68">
         <f t="shared" si="41"/>
         <v>0.28150360639057331</v>
       </c>
-      <c r="AH20" s="69">
+      <c r="AH20" s="68">
         <f>(AH4-AG4)/AG4</f>
         <v>-5.7794881317513272E-2</v>
       </c>
-      <c r="AI20" s="69">
+      <c r="AI20" s="68">
         <f>(AI4-AH4)/AH4</f>
         <v>-1.0880276186398636E-2</v>
       </c>
-      <c r="AJ20" s="69">
+      <c r="AJ20" s="68">
         <f t="shared" ref="AJ20:AT20" si="42">(AJ4-AI4)/AI4</f>
         <v>-4.8452035782501755E-2</v>
       </c>
-      <c r="AK20" s="71">
+      <c r="AK20" s="70">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="69">
+      <c r="AL20" s="68">
         <f t="shared" si="42"/>
         <v>5.0000000000000086E-2</v>
       </c>
-      <c r="AM20" s="69">
+      <c r="AM20" s="68">
         <f t="shared" si="42"/>
         <v>4.9999999999999982E-2</v>
       </c>
-      <c r="AN20" s="69">
+      <c r="AN20" s="68">
         <f t="shared" si="42"/>
         <v>5.0000000000000037E-2</v>
       </c>
-      <c r="AO20" s="69">
+      <c r="AO20" s="68">
         <f t="shared" si="42"/>
         <v>5.0000000000000121E-2</v>
       </c>
-      <c r="AP20" s="69">
+      <c r="AP20" s="68">
         <f t="shared" si="42"/>
         <v>4.9999999999999982E-2</v>
       </c>
-      <c r="AQ20" s="69">
+      <c r="AQ20" s="68">
         <f t="shared" si="42"/>
         <v>4.9999999999999975E-2</v>
       </c>
-      <c r="AR20" s="69">
+      <c r="AR20" s="68">
         <f t="shared" si="42"/>
         <v>5.0000000000000065E-2</v>
       </c>
-      <c r="AS20" s="69">
+      <c r="AS20" s="68">
         <f t="shared" si="42"/>
         <v>4.9999999999999996E-2</v>
       </c>
-      <c r="AT20" s="69">
+      <c r="AT20" s="68">
         <f t="shared" si="42"/>
         <v>5.00000000000001E-2</v>
       </c>
-      <c r="AV20" s="70" t="s">
+      <c r="AV20" s="69" t="s">
         <v>148</v>
       </c>
       <c r="AW20" s="39">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="68"/>
-      <c r="C21" s="69" t="s">
+    <row r="21" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="67"/>
+      <c r="C21" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69">
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68">
         <v>0.17699999999999999</v>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="68">
         <v>0.17199999999999999</v>
       </c>
-      <c r="I21" s="69">
+      <c r="I21" s="68">
         <v>0.128</v>
       </c>
-      <c r="J21" s="69">
+      <c r="J21" s="68">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="K21" s="69">
+      <c r="K21" s="68">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="L21" s="69">
+      <c r="L21" s="68">
         <v>-0.04</v>
       </c>
-      <c r="M21" s="69">
+      <c r="M21" s="68">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="N21" s="69">
+      <c r="N21" s="68">
         <v>1.9E-2</v>
       </c>
-      <c r="O21" s="69">
+      <c r="O21" s="68">
         <v>3.9E-2</v>
       </c>
-      <c r="P21" s="69">
+      <c r="P21" s="68">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q21" s="69">
+      <c r="Q21" s="68">
         <v>1.9E-2</v>
       </c>
-      <c r="R21" s="69">
+      <c r="R21" s="68">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="S21" s="69">
+      <c r="S21" s="68">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="T21" s="69">
+      <c r="T21" s="68">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="U21" s="69">
+      <c r="U21" s="68">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="V21" s="69"/>
-      <c r="W21" s="69"/>
-      <c r="X21" s="69"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="69"/>
-      <c r="AB21" s="69">
+      <c r="V21" s="68"/>
+      <c r="W21" s="68"/>
+      <c r="X21" s="68"/>
+      <c r="Y21" s="68"/>
+      <c r="Z21" s="68"/>
+      <c r="AA21" s="68"/>
+      <c r="AB21" s="68">
         <v>0.1</v>
       </c>
-      <c r="AC21" s="69">
+      <c r="AC21" s="68">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="AD21" s="69">
+      <c r="AD21" s="68">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="AE21" s="69">
+      <c r="AE21" s="68">
         <v>-1.9E-2</v>
       </c>
-      <c r="AF21" s="69">
+      <c r="AF21" s="68">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="AG21" s="69">
+      <c r="AG21" s="68">
         <v>0.157</v>
       </c>
-      <c r="AH21" s="69">
+      <c r="AH21" s="68">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AI21" s="69">
+      <c r="AI21" s="68">
         <v>2E-3</v>
       </c>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="71"/>
-      <c r="AL21" s="69"/>
-      <c r="AM21" s="69"/>
-      <c r="AN21" s="69"/>
-      <c r="AO21" s="69"/>
-      <c r="AP21" s="69"/>
-      <c r="AQ21" s="69"/>
-      <c r="AR21" s="69"/>
-      <c r="AS21" s="69"/>
-      <c r="AT21" s="69"/>
-      <c r="AV21" s="72" t="s">
+      <c r="AJ21" s="68"/>
+      <c r="AK21" s="70"/>
+      <c r="AL21" s="68"/>
+      <c r="AM21" s="68"/>
+      <c r="AN21" s="68"/>
+      <c r="AO21" s="68"/>
+      <c r="AP21" s="68"/>
+      <c r="AQ21" s="68"/>
+      <c r="AR21" s="68"/>
+      <c r="AS21" s="68"/>
+      <c r="AT21" s="68"/>
+      <c r="AV21" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="AW21" s="74">
+      <c r="AW21" s="72">
         <f>NPV(AW19,AK16:KN16)</f>
         <v>222698.69451763167</v>
       </c>
     </row>
-    <row r="22" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="68"/>
-      <c r="C22" s="70" t="s">
+    <row r="22" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="67"/>
+      <c r="C22" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D22" s="69">
         <f t="shared" ref="D22:S22" si="43">D6/D4</f>
         <v>0.22206349669105857</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="69">
         <f t="shared" si="43"/>
         <v>0.24321759076168631</v>
       </c>
-      <c r="F22" s="70">
+      <c r="F22" s="69">
         <f t="shared" si="43"/>
         <v>0.23318955845321498</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G22" s="69">
         <f t="shared" si="43"/>
         <v>0.27947800922766114</v>
       </c>
-      <c r="H22" s="70">
+      <c r="H22" s="69">
         <f t="shared" si="43"/>
         <v>0.26990635046358852</v>
       </c>
-      <c r="I22" s="70">
+      <c r="I22" s="69">
         <f t="shared" si="43"/>
         <v>0.26687912588208512</v>
       </c>
-      <c r="J22" s="70">
+      <c r="J22" s="69">
         <f t="shared" si="43"/>
         <v>0.2759215001378803</v>
       </c>
-      <c r="K22" s="70">
+      <c r="K22" s="69">
         <f t="shared" si="43"/>
         <v>0.32</v>
       </c>
-      <c r="L22" s="70">
+      <c r="L22" s="69">
         <f t="shared" si="43"/>
         <v>0.33190817790530847</v>
       </c>
-      <c r="M22" s="70">
+      <c r="M22" s="69">
         <f t="shared" si="43"/>
         <v>0.33181309227954231</v>
       </c>
-      <c r="N22" s="70">
+      <c r="N22" s="69">
         <f t="shared" si="43"/>
         <v>0.32601863593758618</v>
       </c>
-      <c r="O22" s="70">
+      <c r="O22" s="69">
         <f t="shared" si="43"/>
         <v>0.31937574394921309</v>
       </c>
-      <c r="P22" s="70">
+      <c r="P22" s="69">
         <f t="shared" si="43"/>
         <v>0.32805352241537056</v>
       </c>
-      <c r="Q22" s="70">
+      <c r="Q22" s="69">
         <f t="shared" si="43"/>
         <v>0.33350884891034077</v>
       </c>
-      <c r="R22" s="70">
+      <c r="R22" s="69">
         <f t="shared" si="43"/>
         <v>0.33411282406605464</v>
       </c>
-      <c r="S22" s="70">
+      <c r="S22" s="69">
         <f t="shared" si="43"/>
         <v>0.337080270932411</v>
       </c>
-      <c r="T22" s="70">
+      <c r="T22" s="69">
         <f t="shared" ref="T22:U22" si="44">T6/T4</f>
         <v>0.33411700877113665</v>
       </c>
-      <c r="U22" s="70">
+      <c r="U22" s="69">
         <f t="shared" si="44"/>
         <v>0.32643107726533754</v>
       </c>
-      <c r="Z22" s="70">
+      <c r="Z22" s="69">
         <f t="shared" ref="Z22:AT22" si="45">Z6/Z4</f>
         <v>0.26687237994701529</v>
       </c>
-      <c r="AA22" s="70">
+      <c r="AA22" s="69">
         <f t="shared" si="45"/>
         <v>0.27884786345048301</v>
       </c>
-      <c r="AB22" s="70">
+      <c r="AB22" s="69">
         <f t="shared" si="45"/>
         <v>0.29155722326454031</v>
       </c>
-      <c r="AC22" s="70">
+      <c r="AC22" s="69">
         <f t="shared" si="45"/>
         <v>0.270084388185654</v>
       </c>
-      <c r="AD22" s="70">
+      <c r="AD22" s="69">
         <f t="shared" si="45"/>
         <v>0.29351424694708278</v>
       </c>
-      <c r="AE22" s="70">
+      <c r="AE22" s="69">
         <f t="shared" si="45"/>
         <v>0.32392897036598989</v>
       </c>
-      <c r="AF22" s="70">
+      <c r="AF22" s="69">
         <f t="shared" si="45"/>
         <v>0.28796146618854979</v>
       </c>
-      <c r="AG22" s="70">
+      <c r="AG22" s="69">
         <f t="shared" si="45"/>
         <v>0.23837667202397342</v>
       </c>
-      <c r="AH22" s="70">
+      <c r="AH22" s="69">
         <f t="shared" si="45"/>
         <v>0.30255458826887399</v>
       </c>
-      <c r="AI22" s="70">
+      <c r="AI22" s="69">
         <f t="shared" si="45"/>
         <v>0.32716117241284542</v>
       </c>
-      <c r="AJ22" s="70">
+      <c r="AJ22" s="69">
         <f t="shared" si="45"/>
         <v>0.33317688852946697</v>
       </c>
-      <c r="AK22" s="68">
+      <c r="AK22" s="67">
         <f t="shared" si="45"/>
         <v>0.3299999999999999</v>
       </c>
-      <c r="AL22" s="70">
+      <c r="AL22" s="69">
         <f t="shared" si="45"/>
         <v>0.33</v>
       </c>
-      <c r="AM22" s="70">
+      <c r="AM22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AN22" s="70">
+      <c r="AN22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AO22" s="70">
+      <c r="AO22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AP22" s="70">
+      <c r="AP22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AQ22" s="70">
+      <c r="AQ22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AR22" s="70">
+      <c r="AR22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AS22" s="70">
+      <c r="AS22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AT22" s="70">
+      <c r="AT22" s="69">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AV22" s="70" t="s">
+      <c r="AV22" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="AW22" s="73">
+      <c r="AW22" s="2">
         <v>681.9</v>
       </c>
     </row>
-    <row r="23" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="68"/>
-      <c r="C23" s="70" t="s">
+    <row r="23" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="67"/>
+      <c r="C23" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D23" s="69">
         <f t="shared" ref="D23:R23" si="46">D9/D4</f>
         <v>4.8482551529109935E-2</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="69">
         <f t="shared" si="46"/>
         <v>6.9867383796039975E-2</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F23" s="69">
         <f t="shared" si="46"/>
         <v>6.9410855418983272E-2</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G23" s="69">
         <f t="shared" si="46"/>
         <v>0.11226077697998853</v>
       </c>
-      <c r="H23" s="70">
+      <c r="H23" s="69">
         <f t="shared" si="46"/>
         <v>0.10355029585798817</v>
       </c>
-      <c r="I23" s="70">
+      <c r="I23" s="69">
         <f t="shared" si="46"/>
         <v>9.5948099248804916E-2</v>
       </c>
-      <c r="J23" s="70">
+      <c r="J23" s="69">
         <f t="shared" si="46"/>
         <v>8.417593528816987E-2</v>
       </c>
-      <c r="K23" s="70">
+      <c r="K23" s="69">
         <f t="shared" si="46"/>
         <v>0.1325051194539249</v>
       </c>
-      <c r="L23" s="70">
+      <c r="L23" s="69">
         <f t="shared" si="46"/>
         <v>0.14002869440459109</v>
       </c>
-      <c r="M23" s="70">
+      <c r="M23" s="69">
         <f t="shared" si="46"/>
         <v>0.147417866018516</v>
       </c>
-      <c r="N23" s="70">
+      <c r="N23" s="69">
         <f t="shared" si="46"/>
         <v>0.14034845895131498</v>
       </c>
-      <c r="O23" s="70">
+      <c r="O23" s="69">
         <f t="shared" si="46"/>
         <v>0.13143764052374024</v>
       </c>
-      <c r="P23" s="70">
+      <c r="P23" s="69">
         <f t="shared" si="46"/>
         <v>0.1345494053064959</v>
       </c>
-      <c r="Q23" s="70">
+      <c r="Q23" s="69">
         <f t="shared" si="46"/>
         <v>0.13728243381600116</v>
       </c>
-      <c r="R23" s="70">
+      <c r="R23" s="69">
         <f t="shared" si="46"/>
         <v>0.14596685720884578</v>
       </c>
-      <c r="S23" s="70">
+      <c r="S23" s="69">
         <f>S9/S4</f>
         <v>0.14748522841908057</v>
       </c>
-      <c r="T23" s="70">
+      <c r="T23" s="69">
         <f>T9/T4</f>
         <v>0.13334538987853031</v>
       </c>
-      <c r="U23" s="70">
+      <c r="U23" s="69">
         <f>U9/U4</f>
         <v>0.11705313596303585</v>
       </c>
-      <c r="Z23" s="70">
+      <c r="Z23" s="69">
         <f t="shared" ref="Z23:AT23" si="47">Z9/Z4</f>
         <v>9.8295760208690713E-2</v>
       </c>
-      <c r="AA23" s="70">
+      <c r="AA23" s="69">
         <f t="shared" si="47"/>
         <v>8.897844682826607E-2</v>
       </c>
-      <c r="AB23" s="70">
+      <c r="AB23" s="69">
         <f t="shared" si="47"/>
         <v>0.11485837184825883</v>
       </c>
-      <c r="AC23" s="70">
+      <c r="AC23" s="69">
         <f t="shared" si="47"/>
         <v>9.755274261603375E-2</v>
       </c>
-      <c r="AD23" s="70">
+      <c r="AD23" s="69">
         <f t="shared" si="47"/>
         <v>0.11728629579375847</v>
       </c>
-      <c r="AE23" s="70">
+      <c r="AE23" s="69">
         <f t="shared" si="47"/>
         <v>0.14428510414613313</v>
       </c>
-      <c r="AF23" s="70">
+      <c r="AF23" s="69">
         <f t="shared" si="47"/>
         <v>0.11529782467772244</v>
       </c>
-      <c r="AG23" s="70">
+      <c r="AG23" s="69">
         <f t="shared" si="47"/>
         <v>6.9711153656521932E-2</v>
       </c>
-      <c r="AH23" s="70">
+      <c r="AH23" s="69">
         <f t="shared" si="47"/>
         <v>0.12842939373551618</v>
       </c>
-      <c r="AI23" s="70">
+      <c r="AI23" s="69">
         <f t="shared" si="47"/>
         <v>0.13977711513885643</v>
       </c>
-      <c r="AJ23" s="70">
+      <c r="AJ23" s="69">
         <f t="shared" si="47"/>
         <v>0.14132020159718112</v>
       </c>
-      <c r="AK23" s="68">
+      <c r="AK23" s="67">
         <f t="shared" si="47"/>
         <v>0.13046904559042261</v>
       </c>
-      <c r="AL23" s="70">
+      <c r="AL23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042266</v>
       </c>
-      <c r="AM23" s="70">
+      <c r="AM23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AN23" s="70">
+      <c r="AN23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AO23" s="70">
+      <c r="AO23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042266</v>
       </c>
-      <c r="AP23" s="70">
+      <c r="AP23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AQ23" s="70">
+      <c r="AQ23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AR23" s="70">
+      <c r="AR23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AS23" s="70">
+      <c r="AS23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AT23" s="70">
+      <c r="AT23" s="69">
         <f t="shared" si="47"/>
         <v>0.13046904559042263</v>
       </c>
-      <c r="AV23" s="70" t="s">
+      <c r="AV23" s="69" t="s">
         <v>150</v>
       </c>
       <c r="AW23" s="14">
@@ -8477,211 +8703,211 @@
         <v>326.58556169179013</v>
       </c>
     </row>
-    <row r="24" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="68"/>
-      <c r="C24" s="70" t="s">
+    <row r="24" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="67"/>
+      <c r="C24" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="70">
+      <c r="D24" s="69">
         <f t="shared" ref="D24:S24" si="48">D11/D4</f>
         <v>3.3526719337628644E-2</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="69">
         <f t="shared" si="48"/>
         <v>6.2406074507632685E-2</v>
       </c>
-      <c r="F24" s="70">
+      <c r="F24" s="69">
         <f t="shared" si="48"/>
         <v>6.2105761799097457E-2</v>
       </c>
-      <c r="G24" s="70">
+      <c r="G24" s="69">
         <f t="shared" si="48"/>
         <v>0.10439815446777144</v>
       </c>
-      <c r="H24" s="70">
+      <c r="H24" s="69">
         <f t="shared" si="48"/>
         <v>9.6887667148115364E-2</v>
       </c>
-      <c r="I24" s="70">
+      <c r="I24" s="69">
         <f t="shared" si="48"/>
         <v>8.8800364215797858E-2</v>
       </c>
-      <c r="J24" s="70">
+      <c r="J24" s="69">
         <f t="shared" si="48"/>
         <v>7.0479823513190556E-2</v>
       </c>
-      <c r="K24" s="70">
+      <c r="K24" s="69">
         <f t="shared" si="48"/>
         <v>0.12513310580204778</v>
       </c>
-      <c r="L24" s="70">
+      <c r="L24" s="69">
         <f t="shared" si="48"/>
         <v>0.1308464849354376</v>
       </c>
-      <c r="M24" s="70">
+      <c r="M24" s="69">
         <f t="shared" si="48"/>
         <v>0.14037195837998745</v>
       </c>
-      <c r="N24" s="70">
+      <c r="N24" s="69">
         <f t="shared" si="48"/>
         <v>0.13312565473893145</v>
       </c>
-      <c r="O24" s="70">
+      <c r="O24" s="69">
         <f t="shared" si="48"/>
         <v>0.12429572807829652</v>
       </c>
-      <c r="P24" s="70">
+      <c r="P24" s="69">
         <f t="shared" si="48"/>
         <v>0.12723010064043916</v>
       </c>
-      <c r="Q24" s="70">
+      <c r="Q24" s="69">
         <f t="shared" si="48"/>
         <v>0.13023255813953488</v>
       </c>
-      <c r="R24" s="70">
+      <c r="R24" s="69">
         <f t="shared" si="48"/>
         <v>0.13895144061435419</v>
       </c>
-      <c r="S24" s="70">
+      <c r="S24" s="69">
         <f t="shared" si="48"/>
         <v>0.1407983859345727</v>
       </c>
-      <c r="T24" s="70">
+      <c r="T24" s="69">
         <f t="shared" ref="T24:U24" si="49">T11/T4</f>
         <v>0.12596075594538386</v>
       </c>
-      <c r="U24" s="70">
+      <c r="U24" s="69">
         <f t="shared" si="49"/>
         <v>0.10966601066712302</v>
       </c>
-      <c r="Z24" s="70">
+      <c r="Z24" s="69">
         <f t="shared" ref="Z24:AT24" si="50">Z11/Z4</f>
         <v>9.8295760208690713E-2</v>
       </c>
-      <c r="AA24" s="70">
+      <c r="AA24" s="69">
         <f t="shared" si="50"/>
         <v>8.897844682826607E-2</v>
       </c>
-      <c r="AB24" s="70">
+      <c r="AB24" s="69">
         <f t="shared" si="50"/>
         <v>0.10895529217956344</v>
       </c>
-      <c r="AC24" s="70">
+      <c r="AC24" s="69">
         <f t="shared" si="50"/>
         <v>9.0793248945147675E-2</v>
       </c>
-      <c r="AD24" s="70">
+      <c r="AD24" s="69">
         <f t="shared" si="50"/>
         <v>0.11125411901531304</v>
       </c>
-      <c r="AE24" s="70">
+      <c r="AE24" s="69">
         <f t="shared" si="50"/>
         <v>0.13764044943820225</v>
       </c>
-      <c r="AF24" s="70">
+      <c r="AF24" s="69">
         <f t="shared" si="50"/>
         <v>0.10830659653556746</v>
       </c>
-      <c r="AG24" s="70">
+      <c r="AG24" s="69">
         <f t="shared" si="50"/>
         <v>6.0695510747696461E-2</v>
       </c>
-      <c r="AH24" s="70">
+      <c r="AH24" s="69">
         <f t="shared" si="50"/>
         <v>0.12089271272944742</v>
       </c>
-      <c r="AI24" s="70">
+      <c r="AI24" s="69">
         <f t="shared" si="50"/>
         <v>0.13215066027235375</v>
       </c>
-      <c r="AJ24" s="70">
+      <c r="AJ24" s="69">
         <f t="shared" si="50"/>
         <v>0.13430184701142286</v>
       </c>
-      <c r="AK24" s="68">
+      <c r="AK24" s="67">
         <f t="shared" si="50"/>
         <v>0.1233805074588068</v>
       </c>
-      <c r="AL24" s="70">
+      <c r="AL24" s="69">
         <f t="shared" si="50"/>
         <v>0.12365054700667795</v>
       </c>
-      <c r="AM24" s="70">
+      <c r="AM24" s="69">
         <f t="shared" si="50"/>
         <v>0.1239102993336777</v>
       </c>
-      <c r="AN24" s="70">
+      <c r="AN24" s="69">
         <f t="shared" si="50"/>
         <v>0.12416015633393465</v>
       </c>
-      <c r="AO24" s="70">
+      <c r="AO24" s="69">
         <f t="shared" si="50"/>
         <v>0.12440049497227706</v>
       </c>
-      <c r="AP24" s="70">
+      <c r="AP24" s="69">
         <f t="shared" si="50"/>
         <v>0.12463167785296832</v>
       </c>
-      <c r="AQ24" s="70">
+      <c r="AQ24" s="69">
         <f t="shared" si="50"/>
         <v>0.12485405376677609</v>
       </c>
-      <c r="AR24" s="70">
+      <c r="AR24" s="69">
         <f t="shared" si="50"/>
         <v>0.12506795821720074</v>
       </c>
-      <c r="AS24" s="70">
+      <c r="AS24" s="69">
         <f t="shared" si="50"/>
         <v>0.12527371392665679</v>
       </c>
-      <c r="AT24" s="70">
+      <c r="AT24" s="69">
         <f t="shared" si="50"/>
         <v>0.12547163132337169</v>
       </c>
-      <c r="AV24" s="69" t="s">
+      <c r="AV24" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="AW24" s="69">
+      <c r="AW24" s="68">
         <f>(AW23-B4)/B4</f>
-        <v>0.19628410876113603</v>
-      </c>
-    </row>
-    <row r="25" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="68"/>
-      <c r="C25" s="70" t="s">
+        <v>0.24177019654673054</v>
+      </c>
+    </row>
+    <row r="25" spans="2:49" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="67"/>
+      <c r="C25" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="Z25" s="70">
+      <c r="Z25" s="69">
         <v>0.29199999999999998</v>
       </c>
-      <c r="AA25" s="70">
+      <c r="AA25" s="69">
         <v>0.128</v>
       </c>
-      <c r="AB25" s="70">
+      <c r="AB25" s="69">
         <v>0.13900000000000001</v>
       </c>
-      <c r="AC25" s="70">
+      <c r="AC25" s="69">
         <v>0.153</v>
       </c>
-      <c r="AD25" s="70">
+      <c r="AD25" s="69">
         <v>0.152</v>
       </c>
-      <c r="AE25" s="70">
+      <c r="AE25" s="69">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AF25" s="70">
+      <c r="AF25" s="69">
         <v>0.16300000000000001</v>
       </c>
-      <c r="AG25" s="70">
+      <c r="AG25" s="69">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="AH25" s="70">
+      <c r="AH25" s="69">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AI25" s="70">
+      <c r="AI25" s="69">
         <v>0.16900000000000001</v>
       </c>
-      <c r="AK25" s="68"/>
+      <c r="AK25" s="67"/>
     </row>
     <row r="27" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
@@ -17625,13 +17851,13 @@
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="64" t="s">
         <v>215</v>
       </c>
       <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A5" s="66">
+      <c r="A5" s="65">
         <f>Modell!AK9</f>
         <v>18069.179999999989</v>
       </c>
@@ -17851,15 +18077,15 @@
       </c>
       <c r="D5" s="43">
         <f>Modell!$B$9/Modell!AK9</f>
-        <v>12.049727768498633</v>
+        <v>11.672344843540222</v>
       </c>
       <c r="E5" s="43">
         <f>Modell!$B$9/Modell!AL9</f>
-        <v>11.475931208093929</v>
+        <v>11.11651889860973</v>
       </c>
       <c r="F5" s="43">
         <f>Modell!$B$9/Modell!AM9</f>
-        <v>10.929458293422794</v>
+        <v>10.587160855818794</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -17868,15 +18094,15 @@
       </c>
       <c r="D6" s="35">
         <f>Modell!$B$9/Modell!AK11</f>
-        <v>12.742016660170682</v>
+        <v>12.342952082989521</v>
       </c>
       <c r="E6" s="43">
         <f>Modell!$B$9/Modell!AL11</f>
-        <v>12.108751867474549</v>
+        <v>11.729520379001467</v>
       </c>
       <c r="F6" s="43">
         <f>Modell!$B$9/Modell!AM11</f>
-        <v>11.507969878462227</v>
+        <v>11.147554156505342</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -17885,15 +18111,15 @@
       </c>
       <c r="D7" s="35">
         <f>Modell!$B$4/Modell!AK18</f>
-        <v>13.618078696307126</v>
+        <v>13.119247974830675</v>
       </c>
       <c r="E7" s="43">
         <f>Modell!$B$4/Modell!AL18</f>
-        <v>12.941274544143896</v>
+        <v>12.467235183552544</v>
       </c>
       <c r="F7" s="35">
         <f>Modell!$B$4/Modell!AM18</f>
-        <v>12.299186511778684</v>
+        <v>11.848666859332578</v>
       </c>
     </row>
   </sheetData>
@@ -18159,7 +18385,7 @@
     <row r="6" spans="1:225" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f>AA24</f>
-        <v>-0.29518844566121571</v>
+        <v>-0.26838952724529236</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -20330,7 +20556,7 @@
       </c>
       <c r="AA24" s="16">
         <f>(AA23-Modell!B4)/Modell!B4</f>
-        <v>-0.29518844566121571</v>
+        <v>-0.26838952724529236</v>
       </c>
     </row>
   </sheetData>
